--- a/public/exports-from-60/29188459.xlsx
+++ b/public/exports-from-60/29188459.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t xml:space="preserve">310009811</t>
+          <t xml:space="preserve">310009815</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t xml:space="preserve">310021030</t>
+          <t xml:space="preserve">310021033</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">310021030</t>
+          <t xml:space="preserve">310021033</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">310021030</t>
+          <t xml:space="preserve">310021033</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t xml:space="preserve">310021030</t>
+          <t xml:space="preserve">310021033</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -7114,7 +7114,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t xml:space="preserve">310021030</t>
+          <t xml:space="preserve">310021033</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -7189,7 +7189,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t xml:space="preserve">310021030</t>
+          <t xml:space="preserve">310021033</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">

--- a/public/exports-from-60/29188459.xlsx
+++ b/public/exports-from-60/29188459.xlsx
@@ -5539,7 +5539,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t xml:space="preserve">310009815</t>
+          <t xml:space="preserve">310009811</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t xml:space="preserve">310021033</t>
+          <t xml:space="preserve">310021030</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">310021033</t>
+          <t xml:space="preserve">310021030</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">310021033</t>
+          <t xml:space="preserve">310021030</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t xml:space="preserve">310021033</t>
+          <t xml:space="preserve">310021030</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -7114,7 +7114,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t xml:space="preserve">310021033</t>
+          <t xml:space="preserve">310021030</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -7189,7 +7189,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t xml:space="preserve">310021033</t>
+          <t xml:space="preserve">310021030</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
